--- a/outputs/evaluation/requirement/design/v1/CF_M01/first/CF_M01_req_eval.xlsx
+++ b/outputs/evaluation/requirement/design/v1/CF_M01/first/CF_M01_req_eval.xlsx
@@ -627,10 +627,8 @@
           <t>fixes</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" t="n">
+        <v>0.5667</v>
       </c>
     </row>
   </sheetData>
@@ -763,6 +761,14 @@
           <t>The backend shall be developed using the NestJS framework with TypeScript.</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Changed from Contextualization to Constraint</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Constraint</t>
@@ -776,6 +782,10 @@
           <t>n the case of this project, within the software engineering it will focus on web development technologies and more specifically on the backend. As a framework, NestJS [2] will be used, with the Typescript language [3], and for the infrastructure, AWS cloud services [4] will be used. These technologies are the same as those currently used in the Waapiti company.</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -806,6 +816,14 @@
           <t>The system shall allow authorized users to list the actions performed on platform entities.</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Changed from User Story H6 to FR</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>FR</t>
@@ -820,6 +838,10 @@
 platform entities</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -850,6 +872,14 @@
           <t>The system shall allow authorized users to list the playlogs of the system.</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Changed from User Story H4 to FR</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>FR</t>
@@ -863,6 +893,10 @@
           <t>Be able to list the different playlogs of the system</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -893,6 +927,14 @@
           <t>The system shall allow authorized users to list the connections of the players.</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Changed from User Story H5 to FR</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>FR</t>
@@ -906,6 +948,10 @@
           <t>Be able to list the different player connections in the system</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -941,6 +987,13 @@
           <t>C_01</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Changed from Requisit 12a to QR</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>QR</t>
@@ -956,14 +1009,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>CF_M01_C07</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>CF_M01_C01</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -994,11 +1045,14 @@
           <t>The system shall display all details of the playlog.</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>R_09</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1012,11 +1066,14 @@
           <t>You must be able to see all the details of the playlog.</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>CF_M01_R09</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1047,6 +1104,14 @@
           <t>The system shall store the connections of the players.</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Changed from User Story H2 to FR</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1060,6 +1125,10 @@
           <t>System saves player connections</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1095,6 +1164,13 @@
           <t>C_02</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Changed from Requisit 12d to QR</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1113,11 +1189,9 @@
           <t>CF_M01_C02</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1153,6 +1227,13 @@
           <t>C_05</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Changed from Requisit 15a to QR</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1171,11 +1252,9 @@
           <t>CF_M01_C05</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1206,6 +1285,14 @@
           <t>The system shall store the playlogs of the players.</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Changed from User Story H1 to FR</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1219,6 +1306,10 @@
           <t>System saves the players' playlogs</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1249,11 +1340,14 @@
           <t>All actions must be performed on an entity of the platform.</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>R_06</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1267,11 +1361,14 @@
           <t>All actions are performed on an entity of the platform.</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>CF_M01_R06</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1302,11 +1399,14 @@
           <t>Each action must have a date, client, user, and assigned player.</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>R_06</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1320,11 +1420,14 @@
           <t>Each action has an assigned date, client and player.</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>CF_M01_R06</t>
         </is>
       </c>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1360,6 +1463,13 @@
           <t>C_03</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Changed from Requisit 12f to QR</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1379,11 +1489,9 @@
           <t>CF_M01_C03</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1414,11 +1522,14 @@
           <t>Connections shall only have two states: connected or not connected.</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1432,11 +1543,14 @@
           <t>Connections can only have two states: connected or not connected.</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>CF_M01_R12</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1467,6 +1581,14 @@
           <t>The system shall store the actions performed on the platform.</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Changed from User Story H3 to FR</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1480,6 +1602,10 @@
           <t>System saves the actions carried out on the platform</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1510,11 +1636,14 @@
           <t>The actions visible to the user shall depend on their assigned permissions.</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>R_15</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1528,11 +1657,14 @@
           <t>The actions that the user will be able to see will depend on the permissions it has</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CF_M01_R015</t>
-        </is>
-      </c>
+          <t>CF_M01_R15</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1563,11 +1695,14 @@
           <t>The connections visible to the user shall depend on their assigned permissions.</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1581,11 +1716,14 @@
           <t>The connections that the user will be able to see will depend on the permissions it has.</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>CF_M01_R12</t>
         </is>
       </c>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1616,11 +1754,14 @@
           <t>Users can only observe the confidential data of their own user account.</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>R_28</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1634,11 +1775,14 @@
           <t>Users can only view their confidential data user and no one else.</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CF_M01_R025</t>
-        </is>
-      </c>
+          <t>CF_M01_R25</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1669,11 +1813,14 @@
           <t>Users without permission cannot access data for which they do not have permission.</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>R_26</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1687,11 +1834,14 @@
           <t>Unauthorized users cannot access data they do not own.</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CF_M01_R023</t>
-        </is>
-      </c>
+          <t>CF_M01_R23</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1722,11 +1872,14 @@
           <t>The playlogs visible to the user shall depend on their assigned permissions.</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>R_09</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1740,11 +1893,14 @@
           <t>The playlogs that the user will be able to see will depend on the permissions it has</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>CF_M01_R09</t>
         </is>
       </c>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1775,11 +1931,14 @@
           <t>Each playlog must have a date, client, and assigned player.</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1793,11 +1952,14 @@
           <t>Each playlog has an assigned date, client, player.</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>CF_M01_R01</t>
         </is>
       </c>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1833,6 +1995,13 @@
           <t>C_04</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Changed from Requisit 12g to QR</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1851,11 +2020,9 @@
           <t>CF_M01_C04</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1886,11 +2053,14 @@
           <t>Each connection must have a date, client, and assigned player.</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>R_03</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1904,11 +2074,14 @@
           <t>Each connection has an assigned date, client, player.</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>CF_M01_R03</t>
         </is>
       </c>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1944,6 +2117,13 @@
           <t>C_06</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Changed from Requisit 15c to QR</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1963,11 +2143,9 @@
           <t>CF_M01_C06</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1998,11 +2176,14 @@
           <t>The system scales automatically as data increases.</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>R_24</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -2016,11 +2197,14 @@
           <t>The system scales automatically as they go increasing the data.</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>CF_M01_R24</t>
         </is>
       </c>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2051,11 +2235,14 @@
           <t>The platform scales dynamically with changes in simultaneous connections.</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>R_22</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -2069,11 +2256,14 @@
           <t>The platform scales dynamically with changes in connections simultaneous.</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>CF_M01_R22</t>
         </is>
       </c>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2104,11 +2294,14 @@
           <t>The connection status can only be 'connected' or 'not connected'.</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>R_03</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -2122,11 +2315,14 @@
           <t>The connection status can only be connected or not connected.</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>CF_M01_R03</t>
         </is>
       </c>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2157,11 +2353,14 @@
           <t>Any user must be able to access the platform at any time of the day, except during scheduled updates.</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -2175,11 +2374,14 @@
           <t>Any user must be able to access the platform during any time time of day. Except for scheduled updates.</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>CF_M01_R20</t>
         </is>
       </c>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2210,11 +2412,14 @@
           <t>All actions must be related to an entity of the platform.</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>R_15</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -2228,11 +2433,14 @@
           <t>All actions must be related to an entity the platform.</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CF_M01_R015</t>
-        </is>
-      </c>
+          <t>CF_M01_R15</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2263,11 +2471,14 @@
           <t>The system responds to any user action in less than 5 seconds.</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>R_18</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -2281,11 +2492,14 @@
           <t>The system responds to any user action in less than 5 seconds.</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>CF_M01_R018</t>
-        </is>
-      </c>
+          <t>CF_M01_R18</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
